--- a/docs/seguimiento/tiempos_por_iteracion.xlsx
+++ b/docs/seguimiento/tiempos_por_iteracion.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\Documents\00_materias\proyecto_integrador\dev\GymFlow\docs\seguimiento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2C135C-3922-461A-8B77-95C0D622866A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5857F03-E78B-4CD1-A4AF-4C5DB0A71B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pre" sheetId="2" r:id="rId1"/>
-    <sheet name="Iteracion 1" sheetId="3" r:id="rId2"/>
-    <sheet name="Iteracion 2" sheetId="4" r:id="rId3"/>
-    <sheet name="Iteracion 3" sheetId="5" r:id="rId4"/>
-    <sheet name="Iteracion 4" sheetId="6" r:id="rId5"/>
-    <sheet name="Iteracion 5" sheetId="7" r:id="rId6"/>
-    <sheet name="Hoja1" sheetId="8" r:id="rId7"/>
+    <sheet name="Pre" sheetId="1" r:id="rId1"/>
+    <sheet name="Iteracion 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Iteracion 2" sheetId="3" r:id="rId3"/>
+    <sheet name="Iteracion 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Iteracion 4" sheetId="5" r:id="rId5"/>
+    <sheet name="Iteracion 5" sheetId="6" r:id="rId6"/>
+    <sheet name="Iteracion 6" sheetId="7" r:id="rId7"/>
+    <sheet name="ejemplo_formato" sheetId="8" r:id="rId8"/>
+    <sheet name="Hoja1" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,38 +41,545 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="331">
+  <si>
+    <t>DESARROLLO</t>
+  </si>
+  <si>
+    <t>Hash</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Tiempo (hs)</t>
+  </si>
+  <si>
+    <t>ab57038</t>
+  </si>
+  <si>
+    <t>Documentacion completa para it.6</t>
+  </si>
+  <si>
+    <t>4818cc1</t>
+  </si>
+  <si>
+    <t>RF-23: pago de cuotas online con Mercado Pago</t>
+  </si>
+  <si>
+    <t>88d9632</t>
+  </si>
+  <si>
+    <t>Fix pagos: validar firma segun docs de MP</t>
+  </si>
+  <si>
+    <t>956da94</t>
+  </si>
+  <si>
+    <t>Fix pagos: pedir formato webhook moderno</t>
+  </si>
+  <si>
+    <t>77499d7</t>
+  </si>
+  <si>
+    <t>Pagos: camino IPN sin firma en webhook</t>
+  </si>
+  <si>
+    <t>7158198</t>
+  </si>
+  <si>
+    <t>Fix API: webhook MP acepta IPN legacy</t>
+  </si>
+  <si>
+    <t>198c4f4</t>
+  </si>
+  <si>
+    <t>Correccion nombre RF-21</t>
+  </si>
+  <si>
+    <t>d9f16ad</t>
+  </si>
+  <si>
+    <t>Documento iteracion 6 (parcial)</t>
+  </si>
+  <si>
+    <t>189a84e</t>
+  </si>
+  <si>
+    <t>Plan de pruebas e2e</t>
+  </si>
+  <si>
+    <t>830d2d6</t>
+  </si>
+  <si>
+    <t>Mejoras documentacion iteraciones anteriores</t>
+  </si>
+  <si>
+    <t>8b36e37</t>
+  </si>
+  <si>
+    <t>Ajuste documentacion iteraciones anteriores</t>
+  </si>
+  <si>
+    <t>e26c5d5</t>
+  </si>
+  <si>
+    <t>RF-18: dashboard en tiempo real multi-espacio</t>
+  </si>
+  <si>
+    <t>8f087db</t>
+  </si>
+  <si>
+    <t>Avance en documentacion it.6</t>
+  </si>
+  <si>
+    <t>03caa44</t>
+  </si>
+  <si>
+    <t>Documentacion it.6 completa</t>
+  </si>
+  <si>
+    <t>22cfe25</t>
+  </si>
+  <si>
+    <t>Test de Postman</t>
+  </si>
+  <si>
+    <t>Subtotal Desarrollo</t>
+  </si>
+  <si>
+    <t>OTRAS ACTIVIDADES</t>
+  </si>
+  <si>
+    <t>Actividad</t>
+  </si>
+  <si>
+    <t>Plan de testing</t>
+  </si>
+  <si>
+    <t>Ejecucion plan de testing</t>
+  </si>
+  <si>
+    <t>Documentacion</t>
+  </si>
+  <si>
+    <t>Registro de Tiempos - Pre</t>
+  </si>
+  <si>
+    <t>Autor</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>20d79ab</t>
+  </si>
+  <si>
+    <t>Ignacio</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>CI: pipeline GitHub Actions backend y frontend</t>
+  </si>
+  <si>
+    <t>d929e77</t>
+  </si>
+  <si>
+    <t>Docs: spec, plan de implementacion y README</t>
+  </si>
+  <si>
+    <t>2820d83</t>
+  </si>
+  <si>
+    <t>API: controllers, auth, DI y CORS</t>
+  </si>
+  <si>
+    <t>6d515d4</t>
+  </si>
+  <si>
+    <t>Application layer: DTOs, interfaces, use cases</t>
+  </si>
+  <si>
+    <t>a0dc368</t>
+  </si>
+  <si>
+    <t>Docker setup con PostgreSQL y auto-migracion</t>
+  </si>
+  <si>
+    <t>fd1c1f9</t>
+  </si>
+  <si>
+    <t>Infrastructure: EF Core, repos y configs</t>
+  </si>
+  <si>
+    <t>5fc2abb</t>
+  </si>
+  <si>
+    <t>Crear solucion .NET y proyecto Domain</t>
+  </si>
+  <si>
+    <t>49b5173</t>
+  </si>
+  <si>
+    <t>RF-01/02/04: registro, listado y baja de socio</t>
+  </si>
+  <si>
+    <t>6448ada</t>
+  </si>
+  <si>
+    <t>Frontend: React, TypeScript, Vite, Tailwind</t>
+  </si>
+  <si>
+    <t>eeec743</t>
+  </si>
+  <si>
+    <t>Tests unitarios de Domain y Application</t>
+  </si>
+  <si>
+    <t>41a666b</t>
+  </si>
+  <si>
+    <t>Sebastian</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>TipoDocumento en Socio + validacion cedula UY</t>
+  </si>
+  <si>
+    <t>02cd91d</t>
+  </si>
+  <si>
+    <t>Docs: spec y plan mejoras RF-01</t>
+  </si>
+  <si>
+    <t>8e14117</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>Frontend TipoDocumento en formularios de socio</t>
+  </si>
+  <si>
+    <t>Fix validacion cedula unica + mejoras UI</t>
+  </si>
+  <si>
+    <t>959d9d0</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>RF-22: planes por unidad (CRUD + frontend)</t>
+  </si>
+  <si>
+    <t>b2e5ce1</t>
+  </si>
+  <si>
+    <t>Auditoria: entidad, logger, controller y frontend</t>
+  </si>
+  <si>
+    <t>887ce2f</t>
+  </si>
+  <si>
+    <t>Mover PlanId a UsuarioUnidad + tests</t>
+  </si>
+  <si>
+    <t>a36f79c</t>
+  </si>
+  <si>
+    <t>Docs: spec diseno RF-22 planes por unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Desarrollo - Ignacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Desarrollo - Sebastian</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Subtotal Otras Actividades</t>
+  </si>
+  <si>
+    <t>TOTAL HORAS - Pre</t>
+  </si>
+  <si>
+    <t>Registro de Tiempos - Iteracion 1</t>
+  </si>
+  <si>
+    <t>b6daf11</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>Hotfix: correcciones menores en vista Planes</t>
+  </si>
+  <si>
+    <t>e9b022d</t>
+  </si>
+  <si>
+    <t>Correcciones endpoints + middleware errores</t>
+  </si>
+  <si>
+    <t>ae760f6</t>
+  </si>
+  <si>
+    <t>Sistema de permisos y roles por modulo</t>
+  </si>
+  <si>
+    <t>84117bf</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>Docs: reclasificar RF-23 a RNF-01</t>
+  </si>
+  <si>
+    <t>5965f4b</t>
+  </si>
+  <si>
+    <t>Feat: DTOs y repo para gestion empleados</t>
+  </si>
+  <si>
+    <t>5c790a2</t>
+  </si>
+  <si>
+    <t>Feat: IPasswordHasher con BCrypt</t>
+  </si>
+  <si>
+    <t>a59fb94</t>
+  </si>
+  <si>
+    <t>Feat: entidad Empleado + modulo permisos</t>
+  </si>
+  <si>
+    <t>b3cf9cd</t>
+  </si>
+  <si>
+    <t>Refactor: PasswordHash nullable, limpiar OAuth</t>
+  </si>
+  <si>
+    <t>7570f16</t>
+  </si>
+  <si>
+    <t>Test: tests de Empleado.CambiarRol</t>
+  </si>
+  <si>
+    <t>TOTAL HORAS - Iteracion 1</t>
+  </si>
+  <si>
+    <t>Registro de Tiempos - Iteracion 2</t>
+  </si>
+  <si>
+    <t>ce433d7</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>Correcciones varias</t>
+  </si>
+  <si>
+    <t>3383779</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>Update nombre tutor en README</t>
+  </si>
+  <si>
+    <t>5512577</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>RF-05: portal del socio con perfil</t>
+  </si>
+  <si>
+    <t>18f6f5b</t>
+  </si>
+  <si>
+    <t>Gestion de usuarios desarrollo completo</t>
+  </si>
+  <si>
+    <t>a8b5018</t>
+  </si>
+  <si>
+    <t>Tests automatizados creados y aprobados</t>
+  </si>
+  <si>
+    <t>b687e09</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>Fix: error CS0854 en tests + login socios</t>
+  </si>
+  <si>
+    <t>a9a9cd2</t>
+  </si>
+  <si>
+    <t>Merge PR #3: feature/RF_05</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>Merge PR #4: fix RNF02/RF05</t>
+  </si>
+  <si>
+    <t>509cbdb</t>
+  </si>
+  <si>
+    <t>Ajustes RF-05 y RNF-01</t>
+  </si>
+  <si>
+    <t>bb996ca</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>Desarrollo completo RF-07 (cuotas)</t>
+  </si>
+  <si>
+    <t>b751229</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>RF-06: recordatorios + UX cuotas + responsive</t>
+  </si>
+  <si>
+    <t>a295819</t>
+  </si>
+  <si>
+    <t>Correcciones segun review de RF-07</t>
+  </si>
+  <si>
+    <t>545b483</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>Fix: 3 bloqueantes review (N+1, XSS, SMTP)</t>
+  </si>
+  <si>
+    <t>4c0651c</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>Mejoras en controllers iteracion 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Desarrollo - Franco</t>
+  </si>
+  <si>
+    <t>TOTAL HORAS - Iteracion 2</t>
+  </si>
+  <si>
+    <t>Registro de Tiempos - Iteracion 3</t>
+  </si>
+  <si>
+    <t>5ee5821</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>Merge PRs RF-08/RF-09 + mejoras reqs</t>
+  </si>
+  <si>
+    <t>da840e3</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>RF-08: gestionar clases (CRUD completo)</t>
+  </si>
+  <si>
+    <t>51b00f6</t>
+  </si>
+  <si>
+    <t>RF-09: gestionar horarios semanales</t>
+  </si>
+  <si>
+    <t>d1adf86</t>
+  </si>
+  <si>
+    <t>Fix: bloqueantes code review RF-08</t>
+  </si>
+  <si>
+    <t>ce9a839</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>Merge PR #11: deploy</t>
+  </si>
+  <si>
+    <t>2eb3780</t>
+  </si>
+  <si>
+    <t>Cambios repo para deploy</t>
+  </si>
+  <si>
+    <t>fa20843</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>Eliminar usuarios de vista login</t>
+  </si>
+  <si>
+    <t>8be55e0</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>Correcciones modulo clases e inscripcion</t>
+  </si>
+  <si>
+    <t>1bb7b47</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>Merge PR #14 + trigger CI workflow</t>
+  </si>
+  <si>
+    <t>TOTAL HORAS - Iteracion 3</t>
+  </si>
   <si>
     <t>Registro de Tiempos - Iteracion 4</t>
   </si>
   <si>
-    <t>DESARROLLO</t>
-  </si>
-  <si>
-    <t>Hash</t>
-  </si>
-  <si>
-    <t>Autor</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Descripcion</t>
-  </si>
-  <si>
-    <t>Tiempo (hs)</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
-  </si>
-  <si>
     <t>37e70b5</t>
   </si>
   <si>
-    <t>Sebastian</t>
-  </si>
-  <si>
     <t>2026-05-31</t>
   </si>
   <si>
@@ -80,9 +589,6 @@
     <t>0c545ed</t>
   </si>
   <si>
-    <t>Ignacio</t>
-  </si>
-  <si>
     <t>2026-06-04</t>
   </si>
   <si>
@@ -200,433 +706,19 @@
     <t>Docs: spec y plan login Google (IT5)</t>
   </si>
   <si>
-    <t>Actividad</t>
-  </si>
-  <si>
-    <t>Responsable</t>
-  </si>
-  <si>
     <t>94322c5</t>
   </si>
   <si>
     <t>Login con Google: comando, endpoint y boton UI</t>
   </si>
   <si>
-    <t>Plan de testing</t>
-  </si>
-  <si>
     <t>d79fb7c</t>
   </si>
   <si>
     <t>Email confirmacion al marcar cuota pagada</t>
   </si>
   <si>
-    <t>Ejecucion plan de testing</t>
-  </si>
-  <si>
-    <t>Subtotal Desarrollo</t>
-  </si>
-  <si>
-    <t>Documentacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Desarrollo - Ignacio</t>
-  </si>
-  <si>
-    <t>Subtotal Otras Actividades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Desarrollo - Sebastian</t>
-  </si>
-  <si>
-    <t>OTRAS ACTIVIDADES</t>
-  </si>
-  <si>
     <t>TOTAL HORAS - Iteracion 4</t>
-  </si>
-  <si>
-    <t>Registro de Tiempos - Pre</t>
-  </si>
-  <si>
-    <t>20d79ab</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t>CI: pipeline GitHub Actions backend y frontend</t>
-  </si>
-  <si>
-    <t>d929e77</t>
-  </si>
-  <si>
-    <t>Docs: spec, plan de implementacion y README</t>
-  </si>
-  <si>
-    <t>2820d83</t>
-  </si>
-  <si>
-    <t>API: controllers, auth, DI y CORS</t>
-  </si>
-  <si>
-    <t>6d515d4</t>
-  </si>
-  <si>
-    <t>Application layer: DTOs, interfaces, use cases</t>
-  </si>
-  <si>
-    <t>a0dc368</t>
-  </si>
-  <si>
-    <t>Docker setup con PostgreSQL y auto-migracion</t>
-  </si>
-  <si>
-    <t>fd1c1f9</t>
-  </si>
-  <si>
-    <t>Infrastructure: EF Core, repos y configs</t>
-  </si>
-  <si>
-    <t>5fc2abb</t>
-  </si>
-  <si>
-    <t>Crear solucion .NET y proyecto Domain</t>
-  </si>
-  <si>
-    <t>49b5173</t>
-  </si>
-  <si>
-    <t>RF-01/02/04: registro, listado y baja de socio</t>
-  </si>
-  <si>
-    <t>6448ada</t>
-  </si>
-  <si>
-    <t>Frontend: React, TypeScript, Vite, Tailwind</t>
-  </si>
-  <si>
-    <t>eeec743</t>
-  </si>
-  <si>
-    <t>Tests unitarios de Domain y Application</t>
-  </si>
-  <si>
-    <t>41a666b</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>TipoDocumento en Socio + validacion cedula UY</t>
-  </si>
-  <si>
-    <t>02cd91d</t>
-  </si>
-  <si>
-    <t>Docs: spec y plan mejoras RF-01</t>
-  </si>
-  <si>
-    <t>8e14117</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>Frontend TipoDocumento en formularios de socio</t>
-  </si>
-  <si>
-    <t>Fix validacion cedula unica + mejoras UI</t>
-  </si>
-  <si>
-    <t>959d9d0</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>RF-22: planes por unidad (CRUD + frontend)</t>
-  </si>
-  <si>
-    <t>b2e5ce1</t>
-  </si>
-  <si>
-    <t>Auditoria: entidad, logger, controller y frontend</t>
-  </si>
-  <si>
-    <t>887ce2f</t>
-  </si>
-  <si>
-    <t>Mover PlanId a UsuarioUnidad + tests</t>
-  </si>
-  <si>
-    <t>a36f79c</t>
-  </si>
-  <si>
-    <t>Docs: spec diseno RF-22 planes por unidad</t>
-  </si>
-  <si>
-    <t>TOTAL HORAS - Pre</t>
-  </si>
-  <si>
-    <t>Registro de Tiempos - Iteracion 1</t>
-  </si>
-  <si>
-    <t>b6daf11</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>Hotfix: correcciones menores en vista Planes</t>
-  </si>
-  <si>
-    <t>e9b022d</t>
-  </si>
-  <si>
-    <t>Correcciones endpoints + middleware errores</t>
-  </si>
-  <si>
-    <t>ae760f6</t>
-  </si>
-  <si>
-    <t>Sistema de permisos y roles por modulo</t>
-  </si>
-  <si>
-    <t>84117bf</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>Docs: reclasificar RF-23 a RNF-01</t>
-  </si>
-  <si>
-    <t>5965f4b</t>
-  </si>
-  <si>
-    <t>Feat: DTOs y repo para gestion empleados</t>
-  </si>
-  <si>
-    <t>5c790a2</t>
-  </si>
-  <si>
-    <t>Feat: IPasswordHasher con BCrypt</t>
-  </si>
-  <si>
-    <t>a59fb94</t>
-  </si>
-  <si>
-    <t>Feat: entidad Empleado + modulo permisos</t>
-  </si>
-  <si>
-    <t>b3cf9cd</t>
-  </si>
-  <si>
-    <t>Refactor: PasswordHash nullable, limpiar OAuth</t>
-  </si>
-  <si>
-    <t>7570f16</t>
-  </si>
-  <si>
-    <t>Test: tests de Empleado.CambiarRol</t>
-  </si>
-  <si>
-    <t>TOTAL HORAS - Iteracion 1</t>
-  </si>
-  <si>
-    <t>Registro de Tiempos - Iteracion 2</t>
-  </si>
-  <si>
-    <t>ce433d7</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>Correcciones varias</t>
-  </si>
-  <si>
-    <t>3383779</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>Update nombre tutor en README</t>
-  </si>
-  <si>
-    <t>5512577</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>RF-05: portal del socio con perfil</t>
-  </si>
-  <si>
-    <t>18f6f5b</t>
-  </si>
-  <si>
-    <t>Gestion de usuarios desarrollo completo</t>
-  </si>
-  <si>
-    <t>a8b5018</t>
-  </si>
-  <si>
-    <t>Tests automatizados creados y aprobados</t>
-  </si>
-  <si>
-    <t>b687e09</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>Fix: error CS0854 en tests + login socios</t>
-  </si>
-  <si>
-    <t>a9a9cd2</t>
-  </si>
-  <si>
-    <t>Merge PR #3: feature/RF_05</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>Merge PR #4: fix RNF02/RF05</t>
-  </si>
-  <si>
-    <t>509cbdb</t>
-  </si>
-  <si>
-    <t>Ajustes RF-05 y RNF-01</t>
-  </si>
-  <si>
-    <t>bb996ca</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>Desarrollo completo RF-07 (cuotas)</t>
-  </si>
-  <si>
-    <t>b751229</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>RF-06: recordatorios + UX cuotas + responsive</t>
-  </si>
-  <si>
-    <t>a295819</t>
-  </si>
-  <si>
-    <t>Correcciones segun review de RF-07</t>
-  </si>
-  <si>
-    <t>545b483</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>Fix: 3 bloqueantes review (N+1, XSS, SMTP)</t>
-  </si>
-  <si>
-    <t>4c0651c</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>Mejoras en controllers iteracion 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Desarrollo - Franco</t>
-  </si>
-  <si>
-    <t>TOTAL HORAS - Iteracion 2</t>
-  </si>
-  <si>
-    <t>Registro de Tiempos - Iteracion 3</t>
-  </si>
-  <si>
-    <t>5ee5821</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t>Merge PRs RF-08/RF-09 + mejoras reqs</t>
-  </si>
-  <si>
-    <t>da840e3</t>
-  </si>
-  <si>
-    <t>2026-05-20</t>
-  </si>
-  <si>
-    <t>RF-08: gestionar clases (CRUD completo)</t>
-  </si>
-  <si>
-    <t>51b00f6</t>
-  </si>
-  <si>
-    <t>RF-09: gestionar horarios semanales</t>
-  </si>
-  <si>
-    <t>d1adf86</t>
-  </si>
-  <si>
-    <t>Fix: bloqueantes code review RF-08</t>
-  </si>
-  <si>
-    <t>ce9a839</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>Merge PR #11: deploy</t>
-  </si>
-  <si>
-    <t>2eb3780</t>
-  </si>
-  <si>
-    <t>Cambios repo para deploy</t>
-  </si>
-  <si>
-    <t>fa20843</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>Eliminar usuarios de vista login</t>
-  </si>
-  <si>
-    <t>8be55e0</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>Correcciones modulo clases e inscripcion</t>
-  </si>
-  <si>
-    <t>1bb7b47</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>Merge PR #14 + trigger CI workflow</t>
-  </si>
-  <si>
-    <t>TOTAL HORAS - Iteracion 3</t>
   </si>
   <si>
     <t>Registro de Tiempos - Iteracion 5</t>
@@ -1008,7 +1100,7 @@
       <name val="Consolas"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1025,8 +1117,20 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5496"/>
+        <bgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1073,11 +1177,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1111,6 +1230,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1422,9 +1559,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -1433,449 +1570,449 @@
     <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="E5" s="14">
         <v>0.75</v>
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="E6" s="14">
         <v>2</v>
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E7" s="14">
         <v>1.5</v>
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E8" s="14">
         <v>1.5</v>
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="E9" s="14">
         <v>1.5</v>
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E10" s="14">
         <v>1.5</v>
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E11" s="14">
         <v>1.5</v>
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E12" s="14">
         <v>1.5</v>
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E13" s="14">
         <v>1.5</v>
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="E14" s="14">
         <v>1.5</v>
       </c>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E15" s="14">
         <v>1.5</v>
       </c>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="E16" s="14">
         <v>2</v>
       </c>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="E17" s="14">
         <v>1.5</v>
       </c>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E18" s="14">
         <v>1.5</v>
       </c>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="E19" s="14">
         <v>1.5</v>
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="E20" s="14">
         <v>1.5</v>
       </c>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="E21" s="14">
         <v>1.5</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="E22" s="14">
         <v>2</v>
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D23" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
         <f>SUM(E5:E22)</f>
         <v>27.75</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D24" s="9" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E24" s="10">
         <f>SUMPRODUCT((B5:B22="Ignacio")*(E5:E22))</f>
         <v>19.25</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D25" s="9" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E25" s="10">
         <f>SUMPRODUCT((B5:B22="Sebastian")*(E5:E22))</f>
         <v>8.5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="7"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="7"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="7"/>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B33" s="8" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C33" s="2">
         <f>SUM(C30:C32)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
+    <row r="35" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="26"/>
       <c r="E35" s="12">
         <f>E23+C33</f>
         <v>27.75</v>
@@ -1891,9 +2028,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1902,230 +2039,230 @@
     <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D5" s="14">
         <v>1.5</v>
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D6" s="14">
         <v>1.5</v>
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D7" s="14">
         <v>1.5</v>
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D8" s="14">
         <v>1</v>
       </c>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D9" s="14">
         <v>2.5</v>
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D10" s="14">
         <v>2.5</v>
       </c>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D11" s="14">
         <v>2.5</v>
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D12" s="14">
         <v>1.5</v>
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D13" s="14">
         <v>1.5</v>
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <f>SUM(D5:D13)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <f>SUM(B19:B21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="18"/>
+    <row r="24" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="12">
         <f>D14+B22</f>
         <v>16</v>
@@ -2142,9 +2279,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2153,328 +2290,328 @@
     <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D5" s="14">
         <v>1</v>
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D6" s="14">
         <v>1</v>
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="D7" s="14">
         <v>1.5</v>
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D8" s="14">
         <v>1.5</v>
       </c>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D9" s="14">
         <v>1.5</v>
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="D10" s="14">
         <v>1.25</v>
       </c>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D11" s="14">
         <v>0.25</v>
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="D12" s="14">
         <v>0.25</v>
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="D13" s="14">
         <v>1</v>
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D14" s="14">
         <v>1.5</v>
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D15" s="14">
         <v>1.5</v>
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="D16" s="14">
         <v>1.5</v>
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D17" s="14">
         <v>1.25</v>
       </c>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="D18" s="14">
         <v>1.5</v>
       </c>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C19" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D19" s="2">
         <v>16.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C20" s="9" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="D20" s="10">
         <v>4.75</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C21" s="9" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D21" s="10">
         <v>3.25</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C22" s="9" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D22" s="10">
         <v>8.5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
         <f>SUM(B27:B29)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="18"/>
+    <row r="32" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="25"/>
+      <c r="C32" s="26"/>
       <c r="D32" s="12">
         <f>D19+B30</f>
         <v>16.5</v>
@@ -2491,9 +2628,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2502,230 +2639,230 @@
     <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="D5" s="14">
         <v>0.25</v>
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="D6" s="14">
         <v>1.5</v>
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="D7" s="14">
         <v>1.5</v>
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D8" s="14">
         <v>1.25</v>
       </c>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="D9" s="14">
         <v>0.25</v>
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D10" s="14">
         <v>1</v>
       </c>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D11" s="14">
         <v>1.5</v>
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="D12" s="14">
         <v>1.5</v>
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D13" s="14">
         <v>0.25</v>
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <f>SUM(D5:D13)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <f>SUM(B19:B21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="18"/>
+    <row r="24" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="12">
         <f>D14+B22</f>
         <v>9</v>
@@ -2742,489 +2879,489 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>8</v>
+        <v>178</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="E5" s="14">
         <v>1.5</v>
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="E6" s="14">
         <v>1.25</v>
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="E7" s="14">
         <v>1</v>
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>19</v>
+        <v>187</v>
       </c>
       <c r="E8" s="14">
         <v>1</v>
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="E9" s="14">
         <v>1</v>
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="E10" s="14">
         <v>1</v>
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
+        <v>195</v>
       </c>
       <c r="E12" s="14">
         <v>1</v>
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="E13" s="14">
         <v>1.5</v>
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>198</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="E14" s="14">
         <v>1</v>
       </c>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="E15" s="14">
         <v>1.5</v>
       </c>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>38</v>
+        <v>206</v>
       </c>
       <c r="E16" s="14">
         <v>0.5</v>
       </c>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>39</v>
+        <v>207</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="E17" s="14">
         <v>0.75</v>
       </c>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>41</v>
+        <v>209</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="E18" s="14">
         <v>0.5</v>
       </c>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="E19" s="14">
         <v>0.75</v>
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="E20" s="14">
         <v>1</v>
       </c>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>48</v>
+        <v>216</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="E21" s="14">
         <v>0.25</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:12" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>50</v>
+        <v>218</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="E22" s="14">
         <v>1.25</v>
       </c>
       <c r="F22" s="4"/>
       <c r="I22" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>55</v>
+        <v>221</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c r="E23" s="14">
         <v>1</v>
       </c>
       <c r="F23" s="4"/>
       <c r="I23" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="7"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>59</v>
+        <v>224</v>
       </c>
       <c r="E24" s="14">
         <v>1</v>
       </c>
       <c r="F24" s="4"/>
       <c r="I24" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="7"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D25" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2">
         <f>SUM(E5:E24)</f>
         <v>19.75</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="7"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D26" s="9" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E26" s="10">
         <f>SUMPRODUCT((B5:B24="Ignacio")*(E5:E24))</f>
         <v>14</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="K26" s="2">
         <f>SUM(K23:K25)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D27" s="9" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E27" s="10">
         <f>SUMPRODUCT((B5:B24="Sebastian")*(E5:E24))</f>
         <v>5.75</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="26"/>
       <c r="E37" s="12">
         <f>E25+K26</f>
         <v>19.75</v>
@@ -3241,769 +3378,769 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="E5" s="14">
         <v>2</v>
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="E6" s="14">
         <v>1</v>
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E7" s="14">
         <v>0.75</v>
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="E8" s="14">
         <v>0.75</v>
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="E9" s="14">
         <v>0.75</v>
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="E10" s="14">
         <v>0.75</v>
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="E11" s="14">
         <v>0.75</v>
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="E12" s="14">
         <v>0.75</v>
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="E13" s="14">
         <v>0.5</v>
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="E14" s="14">
         <v>0.25</v>
       </c>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="E15" s="14">
         <v>1</v>
       </c>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="E16" s="14">
         <v>0.75</v>
       </c>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="E17" s="14">
         <v>0.75</v>
       </c>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="E18" s="14">
         <v>1</v>
       </c>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="E19" s="14">
         <v>0.75</v>
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="E20" s="14">
         <v>1</v>
       </c>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="E21" s="14">
         <v>1</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="E22" s="14">
         <v>0.75</v>
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="E23" s="14">
         <v>0.75</v>
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="E24" s="14">
         <v>0.75</v>
       </c>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="E25" s="14">
         <v>0.75</v>
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E26" s="14">
         <v>0.5</v>
       </c>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E27" s="14">
         <v>0.25</v>
       </c>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E28" s="14">
         <v>0.5</v>
       </c>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="E29" s="14">
         <v>0.5</v>
       </c>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="E30" s="14">
         <v>0.75</v>
       </c>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="E31" s="14">
         <v>1</v>
       </c>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="E32" s="14">
         <v>0.5</v>
       </c>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="E33" s="14">
         <v>0.5</v>
       </c>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="E34" s="14">
         <v>0.5</v>
       </c>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="E35" s="14">
         <v>0.75</v>
       </c>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="E36" s="14">
         <v>1</v>
       </c>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="E37" s="14">
         <v>1</v>
       </c>
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="E38" s="14">
         <v>0.5</v>
       </c>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="E39" s="14">
         <v>1</v>
       </c>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D40" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E40" s="2">
         <f>SUM(E5:E39)</f>
         <v>26.75</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D41" s="9" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E41" s="10">
         <f>SUMPRODUCT((B5:B39="Ignacio")*(E5:E39))</f>
         <v>21.25</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="9" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E42" s="10">
         <f>SUMPRODUCT((B5:B39="Sebastian")*(E5:E39))</f>
         <v>5.5</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="7"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="7"/>
       <c r="D48" s="4"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="7"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B50" s="8" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(C47:C49)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="18"/>
+    <row r="52" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="26"/>
       <c r="E52" s="12">
         <f>E40+C50</f>
         <v>26.75</v>
@@ -4015,101 +4152,506 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A5:D31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="45.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="19">
+        <v>46201</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="19">
+        <v>46204</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="21">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="19">
+        <v>46204</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="19">
+        <v>46204</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="21">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="19">
+        <v>46204</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="19">
+        <v>46204</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="19">
+        <v>46208</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="21">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="19">
+        <v>46208</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="19">
+        <v>46208</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="19">
+        <v>46209</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="19">
+        <v>46209</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="19">
+        <v>46210</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="21">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="19">
+        <v>46210</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="19">
+        <v>46211</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="19">
+        <v>46214</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="23">
+        <f>SUM(D7:D21)</f>
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="23">
+        <f>SUM(B28:B30)</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A5:D18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="7"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="7"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
+        <f>SUM(B15:B17)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="B1" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="C3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="B6" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="B7" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="C7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="C8" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
